--- a/cronograma_lavianc2.xlsx
+++ b/cronograma_lavianc2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C2 Proyect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71ECA82-F90B-4FFD-BB12-5E3AFEA05F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE2A15E-26B1-4B99-8B78-117F977282C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Estado Actual" sheetId="1" r:id="rId1"/>
@@ -2883,8 +2883,8 @@
       <c r="F2" s="5">
         <v>1</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>151</v>
+      <c r="G2" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2906,8 +2906,8 @@
       <c r="F3" s="5">
         <v>2</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>151</v>
+      <c r="G3" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -2929,8 +2929,8 @@
       <c r="F4" s="5">
         <v>10</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>151</v>
+      <c r="G4" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -2998,8 +2998,8 @@
       <c r="F7" s="5">
         <v>5</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>151</v>
+      <c r="G7" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3021,8 +3021,8 @@
       <c r="F8" s="5">
         <v>2</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>151</v>
+      <c r="G8" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3044,8 +3044,8 @@
       <c r="F9" s="5">
         <v>2</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>151</v>
+      <c r="G9" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3112,8 +3112,8 @@
       <c r="F2" s="5">
         <v>0.5</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>151</v>
+      <c r="G2" s="8" t="s">
+        <v>163</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>188</v>
